--- a/r1.xlsx
+++ b/r1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>Código</t>
   </si>
@@ -99,19 +99,22 @@
     <t>Raqueta</t>
   </si>
   <si>
+    <t>$99.00000</t>
+  </si>
+  <si>
+    <t>$75.00000</t>
+  </si>
+  <si>
+    <t>Volteck</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>$109.00000</t>
   </si>
   <si>
-    <t>$75.00000</t>
-  </si>
-  <si>
     <t>$327.00000</t>
-  </si>
-  <si>
-    <t>Volteck</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" s="2" customFormat="1">
@@ -638,19 +641,42 @@
         <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
